--- a/2026.02.16_Файлы загрузки и выгрузки данных/Итоги_Fuzzy MoSCoW_Chen 96.xlsx
+++ b/2026.02.16_Файлы загрузки и выгрузки данных/Итоги_Fuzzy MoSCoW_Chen 96.xlsx
@@ -1730,10 +1730,10 @@
         <v>15.81</v>
       </c>
       <c r="F13" t="n">
-        <v>20.655</v>
+        <v>20.65</v>
       </c>
       <c r="G13" t="n">
-        <v>8.32</v>
+        <v>8.31</v>
       </c>
       <c r="H13" t="n">
         <v>12.6</v>
@@ -1745,25 +1745,25 @@
         <v>19.03</v>
       </c>
       <c r="K13" t="n">
-        <v>11.372</v>
+        <v>11.37</v>
       </c>
       <c r="L13" t="n">
-        <v>16.779</v>
+        <v>16.78</v>
       </c>
       <c r="M13" t="n">
-        <v>11.744</v>
+        <v>11.74</v>
       </c>
       <c r="N13" t="n">
-        <v>16.454</v>
+        <v>16.45</v>
       </c>
       <c r="O13" t="n">
-        <v>14.075</v>
+        <v>14.08</v>
       </c>
       <c r="P13" t="n">
-        <v>14.099</v>
+        <v>14.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>14.087</v>
+        <v>14.09</v>
       </c>
     </row>
     <row r="14">
@@ -1776,25 +1776,25 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5.65</v>
+        <v>5.66</v>
       </c>
       <c r="D14" t="n">
-        <v>10.575</v>
+        <v>10.57</v>
       </c>
       <c r="E14" t="n">
-        <v>14.545</v>
+        <v>14.55</v>
       </c>
       <c r="F14" t="n">
-        <v>20.31</v>
+        <v>20.3</v>
       </c>
       <c r="G14" t="n">
-        <v>7.15</v>
+        <v>7.14</v>
       </c>
       <c r="H14" t="n">
-        <v>10.575</v>
+        <v>10.57</v>
       </c>
       <c r="I14" t="n">
-        <v>14.545</v>
+        <v>14.55</v>
       </c>
       <c r="J14" t="n">
         <v>18.36</v>
@@ -1803,22 +1803,22 @@
         <v>9.59</v>
       </c>
       <c r="L14" t="n">
-        <v>15.698</v>
+        <v>15.7</v>
       </c>
       <c r="M14" t="n">
-        <v>9.890000000000001</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>15.308</v>
+        <v>15.31</v>
       </c>
       <c r="O14" t="n">
-        <v>12.644</v>
+        <v>12.64</v>
       </c>
       <c r="P14" t="n">
-        <v>12.599</v>
+        <v>12.6</v>
       </c>
       <c r="Q14" t="n">
-        <v>12.622</v>
+        <v>12.62</v>
       </c>
     </row>
     <row r="15">
@@ -1831,7 +1831,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>5.26</v>
+        <v>5.25</v>
       </c>
       <c r="D15" t="n">
         <v>10.35</v>
@@ -1840,10 +1840,10 @@
         <v>14.66</v>
       </c>
       <c r="F15" t="n">
-        <v>20.655</v>
+        <v>20.66</v>
       </c>
       <c r="G15" t="n">
-        <v>6.835</v>
+        <v>6.83</v>
       </c>
       <c r="H15" t="n">
         <v>10.35</v>
@@ -1855,25 +1855,25 @@
         <v>18.63</v>
       </c>
       <c r="K15" t="n">
-        <v>9.332000000000001</v>
+        <v>9.33</v>
       </c>
       <c r="L15" t="n">
-        <v>15.859</v>
+        <v>15.86</v>
       </c>
       <c r="M15" t="n">
-        <v>9.647</v>
+        <v>9.65</v>
       </c>
       <c r="N15" t="n">
-        <v>15.454</v>
+        <v>15.45</v>
       </c>
       <c r="O15" t="n">
-        <v>12.596</v>
+        <v>12.59</v>
       </c>
       <c r="P15" t="n">
         <v>12.55</v>
       </c>
       <c r="Q15" t="n">
-        <v>12.573</v>
+        <v>12.57</v>
       </c>
     </row>
     <row r="16">
@@ -1889,22 +1889,22 @@
         <v>4.45</v>
       </c>
       <c r="D16" t="n">
-        <v>8.324999999999999</v>
+        <v>8.32</v>
       </c>
       <c r="E16" t="n">
-        <v>13.395</v>
+        <v>13.39</v>
       </c>
       <c r="F16" t="n">
-        <v>20.31</v>
+        <v>20.32</v>
       </c>
       <c r="G16" t="n">
-        <v>5.665</v>
+        <v>5.66</v>
       </c>
       <c r="H16" t="n">
-        <v>8.324999999999999</v>
+        <v>8.32</v>
       </c>
       <c r="I16" t="n">
-        <v>13.395</v>
+        <v>13.39</v>
       </c>
       <c r="J16" t="n">
         <v>17.96</v>
@@ -1913,22 +1913,22 @@
         <v>7.55</v>
       </c>
       <c r="L16" t="n">
-        <v>14.778</v>
+        <v>14.78</v>
       </c>
       <c r="M16" t="n">
-        <v>7.793</v>
+        <v>7.79</v>
       </c>
       <c r="N16" t="n">
-        <v>14.308</v>
+        <v>14.3</v>
       </c>
       <c r="O16" t="n">
-        <v>11.164</v>
+        <v>11.16</v>
       </c>
       <c r="P16" t="n">
-        <v>11.05</v>
+        <v>11.04</v>
       </c>
       <c r="Q16" t="n">
-        <v>11.107</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="17">
@@ -1944,22 +1944,22 @@
         <v>4.45</v>
       </c>
       <c r="D17" t="n">
-        <v>8.324999999999999</v>
+        <v>8.32</v>
       </c>
       <c r="E17" t="n">
-        <v>13.395</v>
+        <v>13.39</v>
       </c>
       <c r="F17" t="n">
-        <v>20.31</v>
+        <v>20.32</v>
       </c>
       <c r="G17" t="n">
-        <v>5.665</v>
+        <v>5.66</v>
       </c>
       <c r="H17" t="n">
-        <v>8.324999999999999</v>
+        <v>8.32</v>
       </c>
       <c r="I17" t="n">
-        <v>13.395</v>
+        <v>13.39</v>
       </c>
       <c r="J17" t="n">
         <v>17.96</v>
@@ -1968,22 +1968,22 @@
         <v>7.55</v>
       </c>
       <c r="L17" t="n">
-        <v>14.778</v>
+        <v>14.78</v>
       </c>
       <c r="M17" t="n">
-        <v>7.793</v>
+        <v>7.79</v>
       </c>
       <c r="N17" t="n">
-        <v>14.308</v>
+        <v>14.3</v>
       </c>
       <c r="O17" t="n">
-        <v>11.164</v>
+        <v>11.16</v>
       </c>
       <c r="P17" t="n">
-        <v>11.05</v>
+        <v>11.04</v>
       </c>
       <c r="Q17" t="n">
-        <v>11.107</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="18">
@@ -1996,7 +1996,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>4.495</v>
+        <v>4.5</v>
       </c>
       <c r="D18" t="n">
         <v>9.09</v>
@@ -2008,7 +2008,7 @@
         <v>17.34</v>
       </c>
       <c r="G18" t="n">
-        <v>5.635</v>
+        <v>5.63</v>
       </c>
       <c r="H18" t="n">
         <v>9.09</v>
@@ -2020,25 +2020,25 @@
         <v>15.83</v>
       </c>
       <c r="K18" t="n">
-        <v>8.170999999999999</v>
+        <v>8.17</v>
       </c>
       <c r="L18" t="n">
-        <v>13.652</v>
+        <v>13.65</v>
       </c>
       <c r="M18" t="n">
-        <v>8.398999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="N18" t="n">
         <v>13.35</v>
       </c>
       <c r="O18" t="n">
-        <v>10.912</v>
+        <v>10.91</v>
       </c>
       <c r="P18" t="n">
-        <v>10.874</v>
+        <v>10.87</v>
       </c>
       <c r="Q18" t="n">
-        <v>10.893</v>
+        <v>10.89</v>
       </c>
     </row>
     <row r="19">
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>4.495</v>
+        <v>4.5</v>
       </c>
       <c r="D19" t="n">
         <v>9.09</v>
@@ -2063,7 +2063,7 @@
         <v>17.34</v>
       </c>
       <c r="G19" t="n">
-        <v>5.635</v>
+        <v>5.63</v>
       </c>
       <c r="H19" t="n">
         <v>9.09</v>
@@ -2075,25 +2075,25 @@
         <v>15.83</v>
       </c>
       <c r="K19" t="n">
-        <v>8.170999999999999</v>
+        <v>8.17</v>
       </c>
       <c r="L19" t="n">
-        <v>13.652</v>
+        <v>13.65</v>
       </c>
       <c r="M19" t="n">
-        <v>8.398999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="N19" t="n">
         <v>13.35</v>
       </c>
       <c r="O19" t="n">
-        <v>10.912</v>
+        <v>10.91</v>
       </c>
       <c r="P19" t="n">
-        <v>10.874</v>
+        <v>10.87</v>
       </c>
       <c r="Q19" t="n">
-        <v>10.893</v>
+        <v>10.89</v>
       </c>
     </row>
     <row r="20">
@@ -2106,46 +2106,46 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4.015</v>
+        <v>4</v>
       </c>
       <c r="D20" t="n">
-        <v>7.425</v>
+        <v>7.43</v>
       </c>
       <c r="E20" t="n">
-        <v>12.705</v>
+        <v>12.71</v>
       </c>
       <c r="F20" t="n">
-        <v>19.965</v>
+        <v>19.96</v>
       </c>
       <c r="G20" t="n">
         <v>5.08</v>
       </c>
       <c r="H20" t="n">
-        <v>7.425</v>
+        <v>7.43</v>
       </c>
       <c r="I20" t="n">
-        <v>12.705</v>
+        <v>12.71</v>
       </c>
       <c r="J20" t="n">
         <v>17.49</v>
       </c>
       <c r="K20" t="n">
-        <v>6.743</v>
+        <v>6.74</v>
       </c>
       <c r="L20" t="n">
-        <v>14.157</v>
+        <v>14.16</v>
       </c>
       <c r="M20" t="n">
-        <v>6.956</v>
+        <v>6.96</v>
       </c>
       <c r="N20" t="n">
-        <v>13.662</v>
+        <v>13.67</v>
       </c>
       <c r="O20" t="n">
         <v>10.45</v>
       </c>
       <c r="P20" t="n">
-        <v>10.309</v>
+        <v>10.31</v>
       </c>
       <c r="Q20" t="n">
         <v>10.38</v>
@@ -2161,49 +2161,49 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2.195</v>
+        <v>2.2</v>
       </c>
       <c r="D21" t="n">
-        <v>6.015</v>
+        <v>6.02</v>
       </c>
       <c r="E21" t="n">
-        <v>10.755</v>
+        <v>10.75</v>
       </c>
       <c r="F21" t="n">
-        <v>16.215</v>
+        <v>16.21</v>
       </c>
       <c r="G21" t="n">
-        <v>3.125</v>
+        <v>3.12</v>
       </c>
       <c r="H21" t="n">
-        <v>6.015</v>
+        <v>6.02</v>
       </c>
       <c r="I21" t="n">
-        <v>10.755</v>
+        <v>10.75</v>
       </c>
       <c r="J21" t="n">
         <v>14.43</v>
       </c>
       <c r="K21" t="n">
-        <v>5.251</v>
+        <v>5.26</v>
       </c>
       <c r="L21" t="n">
-        <v>11.847</v>
+        <v>11.84</v>
       </c>
       <c r="M21" t="n">
-        <v>5.437</v>
+        <v>5.44</v>
       </c>
       <c r="N21" t="n">
         <v>11.49</v>
       </c>
       <c r="O21" t="n">
-        <v>8.548999999999999</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="P21" t="n">
-        <v>8.462999999999999</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="Q21" t="n">
-        <v>8.506</v>
+        <v>8.51</v>
       </c>
     </row>
     <row r="22">
@@ -2216,49 +2216,49 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1.155</v>
+        <v>1.16</v>
       </c>
       <c r="D22" t="n">
-        <v>4.455</v>
+        <v>4.46</v>
       </c>
       <c r="E22" t="n">
-        <v>9.074999999999999</v>
+        <v>9.07</v>
       </c>
       <c r="F22" t="n">
-        <v>14.025</v>
+        <v>14.03</v>
       </c>
       <c r="G22" t="n">
-        <v>1.819</v>
+        <v>1.81</v>
       </c>
       <c r="H22" t="n">
-        <v>4.455</v>
+        <v>4.46</v>
       </c>
       <c r="I22" t="n">
-        <v>9.074999999999999</v>
+        <v>9.07</v>
       </c>
       <c r="J22" t="n">
         <v>12.43</v>
       </c>
       <c r="K22" t="n">
-        <v>3.795</v>
+        <v>3.8</v>
       </c>
       <c r="L22" t="n">
-        <v>10.065</v>
+        <v>10.06</v>
       </c>
       <c r="M22" t="n">
-        <v>3.928</v>
+        <v>3.93</v>
       </c>
       <c r="N22" t="n">
-        <v>9.746</v>
+        <v>9.74</v>
       </c>
       <c r="O22" t="n">
         <v>6.93</v>
       </c>
       <c r="P22" t="n">
-        <v>6.837</v>
+        <v>6.83</v>
       </c>
       <c r="Q22" t="n">
-        <v>6.883</v>
+        <v>6.88</v>
       </c>
     </row>
     <row r="25">
@@ -2342,49 +2342,49 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>7.3</v>
+        <v>7.29</v>
       </c>
       <c r="D28" t="n">
-        <v>13.325</v>
+        <v>13.32</v>
       </c>
       <c r="E28" t="n">
-        <v>18.395</v>
+        <v>18.39</v>
       </c>
       <c r="F28" t="n">
-        <v>25.31</v>
+        <v>25.32</v>
       </c>
       <c r="G28" t="n">
-        <v>9.115</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="H28" t="n">
-        <v>13.325</v>
+        <v>13.32</v>
       </c>
       <c r="I28" t="n">
-        <v>18.395</v>
+        <v>18.39</v>
       </c>
       <c r="J28" t="n">
         <v>22.96</v>
       </c>
       <c r="K28" t="n">
-        <v>12.12</v>
+        <v>12.11</v>
       </c>
       <c r="L28" t="n">
-        <v>19.778</v>
+        <v>19.78</v>
       </c>
       <c r="M28" t="n">
-        <v>12.483</v>
+        <v>12.48</v>
       </c>
       <c r="N28" t="n">
-        <v>19.308</v>
+        <v>19.3</v>
       </c>
       <c r="O28" t="n">
-        <v>15.949</v>
+        <v>15.95</v>
       </c>
       <c r="P28" t="n">
-        <v>15.896</v>
+        <v>15.89</v>
       </c>
       <c r="Q28" t="n">
-        <v>15.922</v>
+        <v>15.92</v>
       </c>
     </row>
     <row r="29">
@@ -2397,49 +2397,49 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>7.3</v>
+        <v>7.29</v>
       </c>
       <c r="D29" t="n">
-        <v>13.325</v>
+        <v>13.32</v>
       </c>
       <c r="E29" t="n">
-        <v>18.395</v>
+        <v>18.39</v>
       </c>
       <c r="F29" t="n">
-        <v>25.31</v>
+        <v>25.32</v>
       </c>
       <c r="G29" t="n">
-        <v>9.115</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="H29" t="n">
-        <v>13.325</v>
+        <v>13.32</v>
       </c>
       <c r="I29" t="n">
-        <v>18.395</v>
+        <v>18.39</v>
       </c>
       <c r="J29" t="n">
         <v>22.96</v>
       </c>
       <c r="K29" t="n">
-        <v>12.12</v>
+        <v>12.11</v>
       </c>
       <c r="L29" t="n">
-        <v>19.778</v>
+        <v>19.78</v>
       </c>
       <c r="M29" t="n">
-        <v>12.483</v>
+        <v>12.48</v>
       </c>
       <c r="N29" t="n">
-        <v>19.308</v>
+        <v>19.3</v>
       </c>
       <c r="O29" t="n">
-        <v>15.949</v>
+        <v>15.95</v>
       </c>
       <c r="P29" t="n">
-        <v>15.896</v>
+        <v>15.89</v>
       </c>
       <c r="Q29" t="n">
-        <v>15.922</v>
+        <v>15.92</v>
       </c>
     </row>
     <row r="30">
@@ -2452,7 +2452,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>6.145</v>
+        <v>6.14</v>
       </c>
       <c r="D30" t="n">
         <v>11.84</v>
@@ -2476,25 +2476,25 @@
         <v>20.43</v>
       </c>
       <c r="K30" t="n">
-        <v>10.701</v>
+        <v>10.7</v>
       </c>
       <c r="L30" t="n">
-        <v>17.732</v>
+        <v>17.73</v>
       </c>
       <c r="M30" t="n">
-        <v>10.992</v>
+        <v>10.99</v>
       </c>
       <c r="N30" t="n">
         <v>17.35</v>
       </c>
       <c r="O30" t="n">
-        <v>14.216</v>
+        <v>14.21</v>
       </c>
       <c r="P30" t="n">
-        <v>14.171</v>
+        <v>14.17</v>
       </c>
       <c r="Q30" t="n">
-        <v>14.194</v>
+        <v>14.19</v>
       </c>
     </row>
     <row r="31">
@@ -2507,7 +2507,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>6.145</v>
+        <v>6.14</v>
       </c>
       <c r="D31" t="n">
         <v>11.84</v>
@@ -2531,25 +2531,25 @@
         <v>20.43</v>
       </c>
       <c r="K31" t="n">
-        <v>10.701</v>
+        <v>10.7</v>
       </c>
       <c r="L31" t="n">
-        <v>17.732</v>
+        <v>17.73</v>
       </c>
       <c r="M31" t="n">
-        <v>10.992</v>
+        <v>10.99</v>
       </c>
       <c r="N31" t="n">
         <v>17.35</v>
       </c>
       <c r="O31" t="n">
-        <v>14.216</v>
+        <v>14.21</v>
       </c>
       <c r="P31" t="n">
-        <v>14.171</v>
+        <v>14.17</v>
       </c>
       <c r="Q31" t="n">
-        <v>14.194</v>
+        <v>14.19</v>
       </c>
     </row>
     <row r="32">
@@ -2562,7 +2562,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>6.145</v>
+        <v>6.14</v>
       </c>
       <c r="D32" t="n">
         <v>11.84</v>
@@ -2586,25 +2586,25 @@
         <v>20.43</v>
       </c>
       <c r="K32" t="n">
-        <v>10.701</v>
+        <v>10.7</v>
       </c>
       <c r="L32" t="n">
-        <v>17.732</v>
+        <v>17.73</v>
       </c>
       <c r="M32" t="n">
-        <v>10.992</v>
+        <v>10.99</v>
       </c>
       <c r="N32" t="n">
         <v>17.35</v>
       </c>
       <c r="O32" t="n">
-        <v>14.216</v>
+        <v>14.21</v>
       </c>
       <c r="P32" t="n">
-        <v>14.171</v>
+        <v>14.17</v>
       </c>
       <c r="Q32" t="n">
-        <v>14.194</v>
+        <v>14.19</v>
       </c>
     </row>
     <row r="33">
@@ -2617,49 +2617,49 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>5.045</v>
+        <v>5.04</v>
       </c>
       <c r="D33" t="n">
-        <v>11.015</v>
+        <v>11.01</v>
       </c>
       <c r="E33" t="n">
-        <v>15.755</v>
+        <v>15.75</v>
       </c>
       <c r="F33" t="n">
-        <v>21.215</v>
+        <v>21.21</v>
       </c>
       <c r="G33" t="n">
-        <v>6.575</v>
+        <v>6.57</v>
       </c>
       <c r="H33" t="n">
-        <v>11.015</v>
+        <v>11.01</v>
       </c>
       <c r="I33" t="n">
-        <v>15.755</v>
+        <v>15.75</v>
       </c>
       <c r="J33" t="n">
         <v>19.43</v>
       </c>
       <c r="K33" t="n">
-        <v>9.821</v>
+        <v>9.82</v>
       </c>
       <c r="L33" t="n">
-        <v>16.847</v>
+        <v>16.84</v>
       </c>
       <c r="M33" t="n">
-        <v>10.127</v>
+        <v>10.12</v>
       </c>
       <c r="N33" t="n">
         <v>16.49</v>
       </c>
       <c r="O33" t="n">
-        <v>13.334</v>
+        <v>13.33</v>
       </c>
       <c r="P33" t="n">
-        <v>13.308</v>
+        <v>13.31</v>
       </c>
       <c r="Q33" t="n">
-        <v>13.321</v>
+        <v>13.32</v>
       </c>
     </row>
     <row r="34">
@@ -2672,49 +2672,49 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>5.045</v>
+        <v>5.04</v>
       </c>
       <c r="D34" t="n">
-        <v>11.015</v>
+        <v>11.01</v>
       </c>
       <c r="E34" t="n">
-        <v>15.755</v>
+        <v>15.75</v>
       </c>
       <c r="F34" t="n">
-        <v>21.215</v>
+        <v>21.21</v>
       </c>
       <c r="G34" t="n">
-        <v>6.575</v>
+        <v>6.57</v>
       </c>
       <c r="H34" t="n">
-        <v>11.015</v>
+        <v>11.01</v>
       </c>
       <c r="I34" t="n">
-        <v>15.755</v>
+        <v>15.75</v>
       </c>
       <c r="J34" t="n">
         <v>19.43</v>
       </c>
       <c r="K34" t="n">
-        <v>9.821</v>
+        <v>9.82</v>
       </c>
       <c r="L34" t="n">
-        <v>16.847</v>
+        <v>16.84</v>
       </c>
       <c r="M34" t="n">
-        <v>10.127</v>
+        <v>10.12</v>
       </c>
       <c r="N34" t="n">
         <v>16.49</v>
       </c>
       <c r="O34" t="n">
-        <v>13.334</v>
+        <v>13.33</v>
       </c>
       <c r="P34" t="n">
-        <v>13.308</v>
+        <v>13.31</v>
       </c>
       <c r="Q34" t="n">
-        <v>13.321</v>
+        <v>13.32</v>
       </c>
     </row>
     <row r="35">
@@ -2727,7 +2727,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>4.22</v>
+        <v>4.21</v>
       </c>
       <c r="D35" t="n">
         <v>9.890000000000001</v>
@@ -2736,10 +2736,10 @@
         <v>15.18</v>
       </c>
       <c r="F35" t="n">
-        <v>21.215</v>
+        <v>21.21</v>
       </c>
       <c r="G35" t="n">
-        <v>5.675</v>
+        <v>5.67</v>
       </c>
       <c r="H35" t="n">
         <v>9.890000000000001</v>
@@ -2751,25 +2751,25 @@
         <v>19.23</v>
       </c>
       <c r="K35" t="n">
-        <v>8.756</v>
+        <v>8.75</v>
       </c>
       <c r="L35" t="n">
-        <v>16.387</v>
+        <v>16.39</v>
       </c>
       <c r="M35" t="n">
-        <v>9.047000000000001</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="N35" t="n">
         <v>15.99</v>
       </c>
       <c r="O35" t="n">
-        <v>12.572</v>
+        <v>12.57</v>
       </c>
       <c r="P35" t="n">
-        <v>12.518</v>
+        <v>12.52</v>
       </c>
       <c r="Q35" t="n">
-        <v>12.545</v>
+        <v>12.54</v>
       </c>
     </row>
     <row r="36">
@@ -2782,7 +2782,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>4.22</v>
+        <v>4.21</v>
       </c>
       <c r="D36" t="n">
         <v>9.890000000000001</v>
@@ -2791,10 +2791,10 @@
         <v>15.18</v>
       </c>
       <c r="F36" t="n">
-        <v>21.215</v>
+        <v>21.22</v>
       </c>
       <c r="G36" t="n">
-        <v>5.675</v>
+        <v>5.67</v>
       </c>
       <c r="H36" t="n">
         <v>9.890000000000001</v>
@@ -2806,25 +2806,25 @@
         <v>19.23</v>
       </c>
       <c r="K36" t="n">
-        <v>8.756</v>
+        <v>8.75</v>
       </c>
       <c r="L36" t="n">
-        <v>16.387</v>
+        <v>16.39</v>
       </c>
       <c r="M36" t="n">
-        <v>9.047000000000001</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="N36" t="n">
         <v>15.99</v>
       </c>
       <c r="O36" t="n">
-        <v>12.572</v>
+        <v>12.57</v>
       </c>
       <c r="P36" t="n">
-        <v>12.518</v>
+        <v>12.52</v>
       </c>
       <c r="Q36" t="n">
-        <v>12.545</v>
+        <v>12.54</v>
       </c>
     </row>
     <row r="37">
@@ -2837,49 +2837,49 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1.155</v>
+        <v>1.16</v>
       </c>
       <c r="D37" t="n">
-        <v>5.555</v>
+        <v>5.55</v>
       </c>
       <c r="E37" t="n">
-        <v>11.275</v>
+        <v>11.28</v>
       </c>
       <c r="F37" t="n">
-        <v>16.775</v>
+        <v>16.77</v>
       </c>
       <c r="G37" t="n">
-        <v>1.965</v>
+        <v>1.96</v>
       </c>
       <c r="H37" t="n">
-        <v>5.555</v>
+        <v>5.55</v>
       </c>
       <c r="I37" t="n">
-        <v>11.275</v>
+        <v>11.28</v>
       </c>
       <c r="J37" t="n">
         <v>15.03</v>
       </c>
       <c r="K37" t="n">
-        <v>4.675</v>
+        <v>4.67</v>
       </c>
       <c r="L37" t="n">
-        <v>12.375</v>
+        <v>12.38</v>
       </c>
       <c r="M37" t="n">
-        <v>4.837</v>
+        <v>4.83</v>
       </c>
       <c r="N37" t="n">
-        <v>12.026</v>
+        <v>12.03</v>
       </c>
       <c r="O37" t="n">
-        <v>8.525</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="P37" t="n">
-        <v>8.430999999999999</v>
+        <v>8.43</v>
       </c>
       <c r="Q37" t="n">
-        <v>8.478</v>
+        <v>8.48</v>
       </c>
     </row>
     <row r="40">
@@ -2963,7 +2963,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>4.825</v>
+        <v>4.81</v>
       </c>
       <c r="D43" t="n">
         <v>9.449999999999999</v>
@@ -2972,10 +2972,10 @@
         <v>13.97</v>
       </c>
       <c r="F43" t="n">
-        <v>20.31</v>
+        <v>20.3</v>
       </c>
       <c r="G43" t="n">
-        <v>6.25</v>
+        <v>6.24</v>
       </c>
       <c r="H43" t="n">
         <v>9.449999999999999</v>
@@ -2987,25 +2987,25 @@
         <v>18.16</v>
       </c>
       <c r="K43" t="n">
-        <v>8.525</v>
+        <v>8.52</v>
       </c>
       <c r="L43" t="n">
-        <v>15.238</v>
+        <v>15.24</v>
       </c>
       <c r="M43" t="n">
         <v>8.81</v>
       </c>
       <c r="N43" t="n">
-        <v>14.808</v>
+        <v>14.81</v>
       </c>
       <c r="O43" t="n">
-        <v>11.881</v>
+        <v>11.88</v>
       </c>
       <c r="P43" t="n">
-        <v>11.809</v>
+        <v>11.81</v>
       </c>
       <c r="Q43" t="n">
-        <v>11.845</v>
+        <v>11.85</v>
       </c>
     </row>
     <row r="44">
@@ -3018,49 +3018,49 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>5.045</v>
+        <v>5.05</v>
       </c>
       <c r="D44" t="n">
-        <v>9.914999999999999</v>
+        <v>9.92</v>
       </c>
       <c r="E44" t="n">
-        <v>13.555</v>
+        <v>13.56</v>
       </c>
       <c r="F44" t="n">
-        <v>18.465</v>
+        <v>18.46</v>
       </c>
       <c r="G44" t="n">
-        <v>6.429</v>
+        <v>6.42</v>
       </c>
       <c r="H44" t="n">
-        <v>9.914999999999999</v>
+        <v>9.92</v>
       </c>
       <c r="I44" t="n">
-        <v>13.555</v>
+        <v>13.56</v>
       </c>
       <c r="J44" t="n">
         <v>16.83</v>
       </c>
       <c r="K44" t="n">
-        <v>8.941000000000001</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="L44" t="n">
-        <v>14.537</v>
+        <v>14.54</v>
       </c>
       <c r="M44" t="n">
-        <v>9.218</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="N44" t="n">
         <v>14.21</v>
       </c>
       <c r="O44" t="n">
-        <v>11.739</v>
+        <v>11.74</v>
       </c>
       <c r="P44" t="n">
-        <v>11.714</v>
+        <v>11.71</v>
       </c>
       <c r="Q44" t="n">
-        <v>11.727</v>
+        <v>11.73</v>
       </c>
     </row>
     <row r="45">
@@ -3073,7 +3073,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>4.22</v>
+        <v>4.21</v>
       </c>
       <c r="D45" t="n">
         <v>8.789999999999999</v>
@@ -3082,10 +3082,10 @@
         <v>12.98</v>
       </c>
       <c r="F45" t="n">
-        <v>18.465</v>
+        <v>18.47</v>
       </c>
       <c r="G45" t="n">
-        <v>5.529</v>
+        <v>5.52</v>
       </c>
       <c r="H45" t="n">
         <v>8.789999999999999</v>
@@ -3097,22 +3097,22 @@
         <v>16.63</v>
       </c>
       <c r="K45" t="n">
-        <v>7.876</v>
+        <v>7.87</v>
       </c>
       <c r="L45" t="n">
-        <v>14.077</v>
+        <v>14.08</v>
       </c>
       <c r="M45" t="n">
-        <v>8.138</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="N45" t="n">
         <v>13.71</v>
       </c>
       <c r="O45" t="n">
-        <v>10.976</v>
+        <v>10.98</v>
       </c>
       <c r="P45" t="n">
-        <v>10.924</v>
+        <v>10.92</v>
       </c>
       <c r="Q45" t="n">
         <v>10.95</v>
@@ -3128,7 +3128,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>4.495</v>
+        <v>4.49</v>
       </c>
       <c r="D46" t="n">
         <v>9.09</v>
@@ -3140,7 +3140,7 @@
         <v>17.34</v>
       </c>
       <c r="G46" t="n">
-        <v>5.635</v>
+        <v>5.63</v>
       </c>
       <c r="H46" t="n">
         <v>9.09</v>
@@ -3152,25 +3152,25 @@
         <v>15.83</v>
       </c>
       <c r="K46" t="n">
-        <v>8.170999999999999</v>
+        <v>8.17</v>
       </c>
       <c r="L46" t="n">
-        <v>13.652</v>
+        <v>13.65</v>
       </c>
       <c r="M46" t="n">
-        <v>8.398999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="N46" t="n">
         <v>13.35</v>
       </c>
       <c r="O46" t="n">
-        <v>10.912</v>
+        <v>10.91</v>
       </c>
       <c r="P46" t="n">
-        <v>10.874</v>
+        <v>10.87</v>
       </c>
       <c r="Q46" t="n">
-        <v>10.893</v>
+        <v>10.89</v>
       </c>
     </row>
     <row r="47">
@@ -3183,7 +3183,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="D47" t="n">
         <v>7.14</v>
@@ -3192,10 +3192,10 @@
         <v>11.33</v>
       </c>
       <c r="F47" t="n">
-        <v>16.215</v>
+        <v>16.21</v>
       </c>
       <c r="G47" t="n">
-        <v>3.71</v>
+        <v>3.7</v>
       </c>
       <c r="H47" t="n">
         <v>7.14</v>
@@ -3207,25 +3207,25 @@
         <v>14.63</v>
       </c>
       <c r="K47" t="n">
-        <v>6.226</v>
+        <v>6.22</v>
       </c>
       <c r="L47" t="n">
-        <v>12.307</v>
+        <v>12.31</v>
       </c>
       <c r="M47" t="n">
-        <v>6.454</v>
+        <v>6.45</v>
       </c>
       <c r="N47" t="n">
         <v>11.99</v>
       </c>
       <c r="O47" t="n">
-        <v>9.266999999999999</v>
+        <v>9.27</v>
       </c>
       <c r="P47" t="n">
-        <v>9.222</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="Q47" t="n">
-        <v>9.244</v>
+        <v>9.24</v>
       </c>
     </row>
     <row r="48">
@@ -3238,7 +3238,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="D48" t="n">
         <v>7.14</v>
@@ -3247,10 +3247,10 @@
         <v>11.33</v>
       </c>
       <c r="F48" t="n">
-        <v>16.215</v>
+        <v>16.21</v>
       </c>
       <c r="G48" t="n">
-        <v>3.71</v>
+        <v>3.7</v>
       </c>
       <c r="H48" t="n">
         <v>7.14</v>
@@ -3262,25 +3262,25 @@
         <v>14.63</v>
       </c>
       <c r="K48" t="n">
-        <v>6.226</v>
+        <v>6.22</v>
       </c>
       <c r="L48" t="n">
-        <v>12.307</v>
+        <v>12.31</v>
       </c>
       <c r="M48" t="n">
-        <v>6.454</v>
+        <v>6.45</v>
       </c>
       <c r="N48" t="n">
         <v>11.99</v>
       </c>
       <c r="O48" t="n">
-        <v>9.266999999999999</v>
+        <v>9.27</v>
       </c>
       <c r="P48" t="n">
-        <v>9.222</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="Q48" t="n">
-        <v>9.244</v>
+        <v>9.24</v>
       </c>
     </row>
     <row r="49">
@@ -3293,49 +3293,49 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>2.195</v>
+        <v>2.2</v>
       </c>
       <c r="D49" t="n">
-        <v>6.015</v>
+        <v>6.01</v>
       </c>
       <c r="E49" t="n">
-        <v>10.755</v>
+        <v>10.76</v>
       </c>
       <c r="F49" t="n">
-        <v>16.215</v>
+        <v>16.22</v>
       </c>
       <c r="G49" t="n">
-        <v>3.125</v>
+        <v>3.12</v>
       </c>
       <c r="H49" t="n">
-        <v>6.015</v>
+        <v>6.01</v>
       </c>
       <c r="I49" t="n">
-        <v>10.755</v>
+        <v>10.76</v>
       </c>
       <c r="J49" t="n">
         <v>14.43</v>
       </c>
       <c r="K49" t="n">
-        <v>5.251</v>
+        <v>5.25</v>
       </c>
       <c r="L49" t="n">
-        <v>11.847</v>
+        <v>11.85</v>
       </c>
       <c r="M49" t="n">
-        <v>5.437</v>
+        <v>5.43</v>
       </c>
       <c r="N49" t="n">
         <v>11.49</v>
       </c>
       <c r="O49" t="n">
-        <v>8.548999999999999</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="P49" t="n">
-        <v>8.462999999999999</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="Q49" t="n">
-        <v>8.506</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="50">
@@ -3348,49 +3348,49 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>2.195</v>
+        <v>2.2</v>
       </c>
       <c r="D50" t="n">
-        <v>6.015</v>
+        <v>6.01</v>
       </c>
       <c r="E50" t="n">
-        <v>10.755</v>
+        <v>10.76</v>
       </c>
       <c r="F50" t="n">
-        <v>16.215</v>
+        <v>16.22</v>
       </c>
       <c r="G50" t="n">
-        <v>3.125</v>
+        <v>3.12</v>
       </c>
       <c r="H50" t="n">
-        <v>6.015</v>
+        <v>6.01</v>
       </c>
       <c r="I50" t="n">
-        <v>10.755</v>
+        <v>10.76</v>
       </c>
       <c r="J50" t="n">
         <v>14.43</v>
       </c>
       <c r="K50" t="n">
-        <v>5.251</v>
+        <v>5.25</v>
       </c>
       <c r="L50" t="n">
-        <v>11.847</v>
+        <v>11.85</v>
       </c>
       <c r="M50" t="n">
-        <v>5.437</v>
+        <v>5.43</v>
       </c>
       <c r="N50" t="n">
         <v>11.49</v>
       </c>
       <c r="O50" t="n">
-        <v>8.548999999999999</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="P50" t="n">
-        <v>8.462999999999999</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="Q50" t="n">
-        <v>8.506</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="51">
@@ -3403,49 +3403,49 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1.155</v>
+        <v>1.16</v>
       </c>
       <c r="D51" t="n">
-        <v>4.455</v>
+        <v>4.46</v>
       </c>
       <c r="E51" t="n">
-        <v>9.074999999999999</v>
+        <v>9.08</v>
       </c>
       <c r="F51" t="n">
-        <v>14.025</v>
+        <v>14.02</v>
       </c>
       <c r="G51" t="n">
-        <v>1.819</v>
+        <v>1.81</v>
       </c>
       <c r="H51" t="n">
-        <v>4.455</v>
+        <v>4.46</v>
       </c>
       <c r="I51" t="n">
-        <v>9.074999999999999</v>
+        <v>9.08</v>
       </c>
       <c r="J51" t="n">
         <v>12.43</v>
       </c>
       <c r="K51" t="n">
-        <v>3.795</v>
+        <v>3.8</v>
       </c>
       <c r="L51" t="n">
-        <v>10.065</v>
+        <v>10.07</v>
       </c>
       <c r="M51" t="n">
-        <v>3.928</v>
+        <v>3.93</v>
       </c>
       <c r="N51" t="n">
-        <v>9.746</v>
+        <v>9.75</v>
       </c>
       <c r="O51" t="n">
-        <v>6.93</v>
+        <v>6.94</v>
       </c>
       <c r="P51" t="n">
-        <v>6.837</v>
+        <v>6.84</v>
       </c>
       <c r="Q51" t="n">
-        <v>6.883</v>
+        <v>6.89</v>
       </c>
     </row>
     <row r="52">
@@ -3458,7 +3458,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>0.605</v>
+        <v>0.6</v>
       </c>
       <c r="D52" t="n">
         <v>3.63</v>
@@ -3470,7 +3470,7 @@
         <v>12.9</v>
       </c>
       <c r="G52" t="n">
-        <v>1.025</v>
+        <v>1.02</v>
       </c>
       <c r="H52" t="n">
         <v>3.63</v>
@@ -3482,22 +3482,22 @@
         <v>11.43</v>
       </c>
       <c r="K52" t="n">
-        <v>3.025</v>
+        <v>3.02</v>
       </c>
       <c r="L52" t="n">
         <v>9.18</v>
       </c>
       <c r="M52" t="n">
-        <v>3.109</v>
+        <v>3.11</v>
       </c>
       <c r="N52" t="n">
-        <v>8.885999999999999</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="O52" t="n">
-        <v>6.103</v>
+        <v>6.1</v>
       </c>
       <c r="P52" t="n">
-        <v>5.997</v>
+        <v>6</v>
       </c>
       <c r="Q52" t="n">
         <v>6.05</v>
@@ -3532,10 +3532,10 @@
         <v>1</v>
       </c>
       <c r="C58" t="n">
-        <v>0.755</v>
+        <v>0.75</v>
       </c>
       <c r="D58" t="n">
-        <v>0.603</v>
+        <v>0.6</v>
       </c>
       <c r="F58" s="13" t="inlineStr">
         <is>
@@ -3546,47 +3546,47 @@
         <v>1</v>
       </c>
       <c r="H58" t="n">
-        <v>0.696</v>
+        <v>0.7</v>
       </c>
       <c r="I58" t="n">
-        <v>0.512</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="59">
       <c r="B59" t="n">
-        <v>0.755</v>
+        <v>0.75</v>
       </c>
       <c r="C59" t="n">
         <v>1</v>
       </c>
       <c r="D59" t="n">
-        <v>0.766</v>
+        <v>0.76</v>
       </c>
       <c r="G59" t="n">
-        <v>0.696</v>
+        <v>0.7</v>
       </c>
       <c r="H59" t="n">
         <v>1</v>
       </c>
       <c r="I59" t="n">
-        <v>0.745</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="60">
       <c r="B60" t="n">
-        <v>0.603</v>
+        <v>0.6</v>
       </c>
       <c r="C60" t="n">
-        <v>0.766</v>
+        <v>0.76</v>
       </c>
       <c r="D60" t="n">
         <v>1</v>
       </c>
       <c r="G60" t="n">
-        <v>0.512</v>
+        <v>0.51</v>
       </c>
       <c r="H60" t="n">
-        <v>0.745</v>
+        <v>0.75</v>
       </c>
       <c r="I60" t="n">
         <v>1</v>
@@ -3605,7 +3605,7 @@
         <v>0.73</v>
       </c>
       <c r="D62" t="n">
-        <v>0.824</v>
+        <v>0.82</v>
       </c>
       <c r="F62" s="13" t="inlineStr">
         <is>
@@ -3616,10 +3616,10 @@
         <v>1</v>
       </c>
       <c r="H62" t="n">
-        <v>0.698</v>
+        <v>0.7</v>
       </c>
       <c r="I62" t="n">
-        <v>0.796</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="63">
@@ -3630,33 +3630,33 @@
         <v>1</v>
       </c>
       <c r="D63" t="n">
-        <v>0.606</v>
+        <v>0.61</v>
       </c>
       <c r="G63" t="n">
-        <v>0.698</v>
+        <v>0.7</v>
       </c>
       <c r="H63" t="n">
         <v>1</v>
       </c>
       <c r="I63" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="64">
       <c r="B64" t="n">
-        <v>0.824</v>
+        <v>0.82</v>
       </c>
       <c r="C64" t="n">
-        <v>0.606</v>
+        <v>0.61</v>
       </c>
       <c r="D64" t="n">
         <v>1</v>
       </c>
       <c r="G64" t="n">
-        <v>0.796</v>
+        <v>0.8</v>
       </c>
       <c r="H64" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I64" t="n">
         <v>1</v>
@@ -3672,10 +3672,10 @@
         <v>1</v>
       </c>
       <c r="C66" t="n">
-        <v>0.375</v>
+        <v>0.37</v>
       </c>
       <c r="D66" t="n">
-        <v>0.805</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="F66" s="13" t="inlineStr">
         <is>
@@ -3686,47 +3686,47 @@
         <v>1</v>
       </c>
       <c r="H66" t="n">
-        <v>0.271</v>
+        <v>0.27</v>
       </c>
       <c r="I66" t="n">
-        <v>0.739</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="67">
       <c r="B67" t="n">
-        <v>0.375</v>
+        <v>0.37</v>
       </c>
       <c r="C67" t="n">
         <v>1</v>
       </c>
       <c r="D67" t="n">
-        <v>0.464</v>
+        <v>0.46</v>
       </c>
       <c r="G67" t="n">
-        <v>0.271</v>
+        <v>0.27</v>
       </c>
       <c r="H67" t="n">
         <v>1</v>
       </c>
       <c r="I67" t="n">
-        <v>0.378</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="68">
       <c r="B68" t="n">
-        <v>0.805</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="C68" t="n">
-        <v>0.464</v>
+        <v>0.46</v>
       </c>
       <c r="D68" t="n">
         <v>1</v>
       </c>
       <c r="G68" t="n">
-        <v>0.739</v>
+        <v>0.74</v>
       </c>
       <c r="H68" t="n">
-        <v>0.378</v>
+        <v>0.38</v>
       </c>
       <c r="I68" t="n">
         <v>1</v>
@@ -3742,10 +3742,10 @@
         <v>1</v>
       </c>
       <c r="C70" t="n">
-        <v>0.743</v>
+        <v>0.74</v>
       </c>
       <c r="D70" t="n">
-        <v>0.403</v>
+        <v>0.4</v>
       </c>
       <c r="F70" s="13" t="inlineStr">
         <is>
@@ -3756,47 +3756,47 @@
         <v>1</v>
       </c>
       <c r="H70" t="n">
-        <v>0.698</v>
+        <v>0.7</v>
       </c>
       <c r="I70" t="n">
-        <v>0.314</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="71">
       <c r="B71" t="n">
-        <v>0.743</v>
+        <v>0.74</v>
       </c>
       <c r="C71" t="n">
         <v>1</v>
       </c>
       <c r="D71" t="n">
-        <v>0.297</v>
+        <v>0.3</v>
       </c>
       <c r="G71" t="n">
-        <v>0.698</v>
+        <v>0.7</v>
       </c>
       <c r="H71" t="n">
         <v>1</v>
       </c>
       <c r="I71" t="n">
-        <v>0.213</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="72">
       <c r="B72" t="n">
-        <v>0.403</v>
+        <v>0.4</v>
       </c>
       <c r="C72" t="n">
-        <v>0.297</v>
+        <v>0.3</v>
       </c>
       <c r="D72" t="n">
         <v>1</v>
       </c>
       <c r="G72" t="n">
-        <v>0.314</v>
+        <v>0.31</v>
       </c>
       <c r="H72" t="n">
-        <v>0.213</v>
+        <v>0.21</v>
       </c>
       <c r="I72" t="n">
         <v>1</v>
@@ -3812,10 +3812,10 @@
         <v>1</v>
       </c>
       <c r="C74" t="n">
-        <v>0.423</v>
+        <v>0.42</v>
       </c>
       <c r="D74" t="n">
-        <v>0.616</v>
+        <v>0.62</v>
       </c>
       <c r="F74" s="13" t="inlineStr">
         <is>
@@ -3826,47 +3826,47 @@
         <v>1</v>
       </c>
       <c r="H74" t="n">
-        <v>0.326</v>
+        <v>0.33</v>
       </c>
       <c r="I74" t="n">
-        <v>0.584</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="75">
       <c r="B75" t="n">
-        <v>0.423</v>
+        <v>0.42</v>
       </c>
       <c r="C75" t="n">
         <v>1</v>
       </c>
       <c r="D75" t="n">
-        <v>0.217</v>
+        <v>0.22</v>
       </c>
       <c r="G75" t="n">
-        <v>0.326</v>
+        <v>0.33</v>
       </c>
       <c r="H75" t="n">
         <v>1</v>
       </c>
       <c r="I75" t="n">
-        <v>0.135</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="76">
       <c r="B76" t="n">
-        <v>0.616</v>
+        <v>0.62</v>
       </c>
       <c r="C76" t="n">
-        <v>0.217</v>
+        <v>0.22</v>
       </c>
       <c r="D76" t="n">
         <v>1</v>
       </c>
       <c r="G76" t="n">
-        <v>0.584</v>
+        <v>0.58</v>
       </c>
       <c r="H76" t="n">
-        <v>0.135</v>
+        <v>0.14</v>
       </c>
       <c r="I76" t="n">
         <v>1</v>
@@ -3882,10 +3882,10 @@
         <v>1</v>
       </c>
       <c r="C78" t="n">
-        <v>0.477</v>
+        <v>0.48</v>
       </c>
       <c r="D78" t="n">
-        <v>0.389</v>
+        <v>0.39</v>
       </c>
       <c r="F78" s="13" t="inlineStr">
         <is>
@@ -3896,47 +3896,47 @@
         <v>1</v>
       </c>
       <c r="H78" t="n">
-        <v>0.409</v>
+        <v>0.41</v>
       </c>
       <c r="I78" t="n">
-        <v>0.304</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="79">
       <c r="B79" t="n">
-        <v>0.477</v>
+        <v>0.48</v>
       </c>
       <c r="C79" t="n">
         <v>1</v>
       </c>
       <c r="D79" t="n">
-        <v>0.179</v>
+        <v>0.18</v>
       </c>
       <c r="G79" t="n">
-        <v>0.409</v>
+        <v>0.41</v>
       </c>
       <c r="H79" t="n">
         <v>1</v>
       </c>
       <c r="I79" t="n">
-        <v>0.103</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="80">
       <c r="B80" t="n">
-        <v>0.389</v>
+        <v>0.39</v>
       </c>
       <c r="C80" t="n">
-        <v>0.179</v>
+        <v>0.18</v>
       </c>
       <c r="D80" t="n">
         <v>1</v>
       </c>
       <c r="G80" t="n">
-        <v>0.304</v>
+        <v>0.3</v>
       </c>
       <c r="H80" t="n">
-        <v>0.103</v>
+        <v>0.1</v>
       </c>
       <c r="I80" t="n">
         <v>1</v>
@@ -3952,10 +3952,10 @@
         <v>1</v>
       </c>
       <c r="C82" t="n">
-        <v>0.477</v>
+        <v>0.48</v>
       </c>
       <c r="D82" t="n">
-        <v>0.612</v>
+        <v>0.61</v>
       </c>
       <c r="F82" s="13" t="inlineStr">
         <is>
@@ -3966,47 +3966,47 @@
         <v>1</v>
       </c>
       <c r="H82" t="n">
-        <v>0.409</v>
+        <v>0.41</v>
       </c>
       <c r="I82" t="n">
-        <v>0.539</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="83">
       <c r="B83" t="n">
-        <v>0.477</v>
+        <v>0.48</v>
       </c>
       <c r="C83" t="n">
         <v>1</v>
       </c>
       <c r="D83" t="n">
-        <v>0.297</v>
+        <v>0.3</v>
       </c>
       <c r="G83" t="n">
-        <v>0.409</v>
+        <v>0.41</v>
       </c>
       <c r="H83" t="n">
         <v>1</v>
       </c>
       <c r="I83" t="n">
-        <v>0.213</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="84">
       <c r="B84" t="n">
-        <v>0.612</v>
+        <v>0.61</v>
       </c>
       <c r="C84" t="n">
-        <v>0.297</v>
+        <v>0.3</v>
       </c>
       <c r="D84" t="n">
         <v>1</v>
       </c>
       <c r="G84" t="n">
-        <v>0.539</v>
+        <v>0.54</v>
       </c>
       <c r="H84" t="n">
-        <v>0.213</v>
+        <v>0.21</v>
       </c>
       <c r="I84" t="n">
         <v>1</v>
@@ -4022,10 +4022,10 @@
         <v>1</v>
       </c>
       <c r="C86" t="n">
-        <v>0.884</v>
+        <v>0.88</v>
       </c>
       <c r="D86" t="n">
-        <v>0.665</v>
+        <v>0.67</v>
       </c>
       <c r="F86" s="13" t="inlineStr">
         <is>
@@ -4036,24 +4036,24 @@
         <v>1</v>
       </c>
       <c r="H86" t="n">
-        <v>0.855</v>
+        <v>0.85</v>
       </c>
       <c r="I86" t="n">
-        <v>0.613</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="87">
       <c r="B87" t="n">
-        <v>0.884</v>
+        <v>0.88</v>
       </c>
       <c r="C87" t="n">
         <v>1</v>
       </c>
       <c r="D87" t="n">
-        <v>0.694</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G87" t="n">
-        <v>0.855</v>
+        <v>0.85</v>
       </c>
       <c r="H87" t="n">
         <v>1</v>
@@ -4064,16 +4064,16 @@
     </row>
     <row r="88">
       <c r="B88" t="n">
-        <v>0.665</v>
+        <v>0.67</v>
       </c>
       <c r="C88" t="n">
-        <v>0.694</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="D88" t="n">
         <v>1</v>
       </c>
       <c r="G88" t="n">
-        <v>0.613</v>
+        <v>0.61</v>
       </c>
       <c r="H88" t="n">
         <v>0.66</v>
@@ -4092,10 +4092,10 @@
         <v>1</v>
       </c>
       <c r="C90" t="n">
-        <v>0.729</v>
+        <v>0.73</v>
       </c>
       <c r="D90" t="n">
-        <v>0.616</v>
+        <v>0.62</v>
       </c>
       <c r="F90" s="13" t="inlineStr">
         <is>
@@ -4106,47 +4106,47 @@
         <v>1</v>
       </c>
       <c r="H90" t="n">
-        <v>0.649</v>
+        <v>0.65</v>
       </c>
       <c r="I90" t="n">
-        <v>0.584</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="91">
       <c r="B91" t="n">
-        <v>0.729</v>
+        <v>0.73</v>
       </c>
       <c r="C91" t="n">
         <v>1</v>
       </c>
       <c r="D91" t="n">
-        <v>0.421</v>
+        <v>0.42</v>
       </c>
       <c r="G91" t="n">
-        <v>0.649</v>
+        <v>0.65</v>
       </c>
       <c r="H91" t="n">
         <v>1</v>
       </c>
       <c r="I91" t="n">
-        <v>0.344</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="92">
       <c r="B92" t="n">
-        <v>0.616</v>
+        <v>0.62</v>
       </c>
       <c r="C92" t="n">
-        <v>0.421</v>
+        <v>0.42</v>
       </c>
       <c r="D92" t="n">
         <v>1</v>
       </c>
       <c r="G92" t="n">
-        <v>0.584</v>
+        <v>0.58</v>
       </c>
       <c r="H92" t="n">
-        <v>0.344</v>
+        <v>0.34</v>
       </c>
       <c r="I92" t="n">
         <v>1</v>
@@ -4165,7 +4165,7 @@
         <v>0.38</v>
       </c>
       <c r="D94" t="n">
-        <v>0.601</v>
+        <v>0.6</v>
       </c>
       <c r="F94" s="13" t="inlineStr">
         <is>
@@ -4176,10 +4176,10 @@
         <v>1</v>
       </c>
       <c r="H94" t="n">
-        <v>0.292</v>
+        <v>0.29</v>
       </c>
       <c r="I94" t="n">
-        <v>0.531</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="95">
@@ -4190,33 +4190,33 @@
         <v>1</v>
       </c>
       <c r="D95" t="n">
-        <v>0.642</v>
+        <v>0.64</v>
       </c>
       <c r="G95" t="n">
-        <v>0.292</v>
+        <v>0.29</v>
       </c>
       <c r="H95" t="n">
         <v>1</v>
       </c>
       <c r="I95" t="n">
-        <v>0.576</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="96">
       <c r="B96" t="n">
-        <v>0.601</v>
+        <v>0.6</v>
       </c>
       <c r="C96" t="n">
-        <v>0.642</v>
+        <v>0.64</v>
       </c>
       <c r="D96" t="n">
         <v>1</v>
       </c>
       <c r="G96" t="n">
-        <v>0.531</v>
+        <v>0.53</v>
       </c>
       <c r="H96" t="n">
-        <v>0.576</v>
+        <v>0.58</v>
       </c>
       <c r="I96" t="n">
         <v>1</v>
@@ -4248,13 +4248,13 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.6787029999999999</v>
+        <v>0.68</v>
       </c>
       <c r="C102" t="n">
-        <v>0.760147</v>
+        <v>0.76</v>
       </c>
       <c r="D102" t="n">
-        <v>0.684094</v>
+        <v>0.68</v>
       </c>
       <c r="F102" s="13" t="inlineStr">
         <is>
@@ -4262,13 +4262,13 @@
         </is>
       </c>
       <c r="G102" t="n">
-        <v>0.6036820000000001</v>
+        <v>0.6</v>
       </c>
       <c r="H102" t="n">
-        <v>0.720355</v>
+        <v>0.72</v>
       </c>
       <c r="I102" t="n">
-        <v>0.628405</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="103">
@@ -4278,13 +4278,13 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.77707</v>
+        <v>0.78</v>
       </c>
       <c r="C103" t="n">
-        <v>0.668366</v>
+        <v>0.67</v>
       </c>
       <c r="D103" t="n">
-        <v>0.715044</v>
+        <v>0.71</v>
       </c>
       <c r="F103" s="13" t="inlineStr">
         <is>
@@ -4292,13 +4292,13 @@
         </is>
       </c>
       <c r="G103" t="n">
-        <v>0.746888</v>
+        <v>0.75</v>
       </c>
       <c r="H103" t="n">
-        <v>0.629915</v>
+        <v>0.63</v>
       </c>
       <c r="I103" t="n">
-        <v>0.678636</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="104">
@@ -4308,13 +4308,13 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.589966</v>
+        <v>0.59</v>
       </c>
       <c r="C104" t="n">
-        <v>0.419265</v>
+        <v>0.42</v>
       </c>
       <c r="D104" t="n">
-        <v>0.634684</v>
+        <v>0.63</v>
       </c>
       <c r="F104" s="13" t="inlineStr">
         <is>
@@ -4322,13 +4322,13 @@
         </is>
       </c>
       <c r="G104" t="n">
-        <v>0.504643</v>
+        <v>0.51</v>
       </c>
       <c r="H104" t="n">
-        <v>0.324195</v>
+        <v>0.32</v>
       </c>
       <c r="I104" t="n">
-        <v>0.558151</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="105">
@@ -4338,13 +4338,13 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.5733</v>
+        <v>0.57</v>
       </c>
       <c r="C105" t="n">
-        <v>0.520184</v>
+        <v>0.52</v>
       </c>
       <c r="D105" t="n">
-        <v>0.350149</v>
+        <v>0.35</v>
       </c>
       <c r="F105" s="13" t="inlineStr">
         <is>
@@ -4352,13 +4352,13 @@
         </is>
       </c>
       <c r="G105" t="n">
-        <v>0.506059</v>
+        <v>0.51</v>
       </c>
       <c r="H105" t="n">
-        <v>0.455409</v>
+        <v>0.46</v>
       </c>
       <c r="I105" t="n">
-        <v>0.263257</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="106">
@@ -4368,13 +4368,13 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.519218</v>
+        <v>0.52</v>
       </c>
       <c r="C106" t="n">
-        <v>0.319753</v>
+        <v>0.32</v>
       </c>
       <c r="D106" t="n">
-        <v>0.41608</v>
+        <v>0.42</v>
       </c>
       <c r="F106" s="13" t="inlineStr">
         <is>
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="G106" t="n">
-        <v>0.454771</v>
+        <v>0.45</v>
       </c>
       <c r="H106" t="n">
-        <v>0.230446</v>
+        <v>0.23</v>
       </c>
       <c r="I106" t="n">
-        <v>0.359436</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="107">
@@ -4398,13 +4398,13 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.433006</v>
+        <v>0.43</v>
       </c>
       <c r="C107" t="n">
-        <v>0.327993</v>
+        <v>0.33</v>
       </c>
       <c r="D107" t="n">
-        <v>0.283991</v>
+        <v>0.28</v>
       </c>
       <c r="F107" s="13" t="inlineStr">
         <is>
@@ -4412,13 +4412,13 @@
         </is>
       </c>
       <c r="G107" t="n">
-        <v>0.356736</v>
+        <v>0.36</v>
       </c>
       <c r="H107" t="n">
-        <v>0.256281</v>
+        <v>0.26</v>
       </c>
       <c r="I107" t="n">
-        <v>0.203774</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="108">
@@ -4428,13 +4428,13 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.5446569999999999</v>
+        <v>0.54</v>
       </c>
       <c r="C108" t="n">
-        <v>0.38702</v>
+        <v>0.39</v>
       </c>
       <c r="D108" t="n">
-        <v>0.454669</v>
+        <v>0.46</v>
       </c>
       <c r="F108" s="13" t="inlineStr">
         <is>
@@ -4442,13 +4442,13 @@
         </is>
       </c>
       <c r="G108" t="n">
-        <v>0.473932</v>
+        <v>0.47</v>
       </c>
       <c r="H108" t="n">
-        <v>0.310925</v>
+        <v>0.31</v>
       </c>
       <c r="I108" t="n">
-        <v>0.375613</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="109">
@@ -4458,13 +4458,13 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.774833</v>
+        <v>0.77</v>
       </c>
       <c r="C109" t="n">
-        <v>0.789347</v>
+        <v>0.79</v>
       </c>
       <c r="D109" t="n">
-        <v>0.679953</v>
+        <v>0.68</v>
       </c>
       <c r="F109" s="13" t="inlineStr">
         <is>
@@ -4472,13 +4472,13 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>0.733658</v>
+        <v>0.73</v>
       </c>
       <c r="H109" t="n">
-        <v>0.757375</v>
+        <v>0.76</v>
       </c>
       <c r="I109" t="n">
-        <v>0.6364300000000001</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="110">
@@ -4488,13 +4488,13 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.672414</v>
+        <v>0.67</v>
       </c>
       <c r="C110" t="n">
-        <v>0.575298</v>
+        <v>0.58</v>
       </c>
       <c r="D110" t="n">
-        <v>0.518429</v>
+        <v>0.52</v>
       </c>
       <c r="F110" s="13" t="inlineStr">
         <is>
@@ -4502,13 +4502,13 @@
         </is>
       </c>
       <c r="G110" t="n">
-        <v>0.616603</v>
+        <v>0.62</v>
       </c>
       <c r="H110" t="n">
-        <v>0.496697</v>
+        <v>0.5</v>
       </c>
       <c r="I110" t="n">
-        <v>0.463855</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="111">
@@ -4518,13 +4518,13 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.490224</v>
+        <v>0.49</v>
       </c>
       <c r="C111" t="n">
-        <v>0.510871</v>
+        <v>0.51</v>
       </c>
       <c r="D111" t="n">
-        <v>0.621465</v>
+        <v>0.62</v>
       </c>
       <c r="F111" s="13" t="inlineStr">
         <is>
@@ -4532,13 +4532,13 @@
         </is>
       </c>
       <c r="G111" t="n">
-        <v>0.411425</v>
+        <v>0.41</v>
       </c>
       <c r="H111" t="n">
-        <v>0.43404</v>
+        <v>0.43</v>
       </c>
       <c r="I111" t="n">
-        <v>0.553441</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="114">
@@ -4555,13 +4555,13 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.641192</v>
+        <v>0.64</v>
       </c>
       <c r="C116" t="n">
-        <v>0.740251</v>
+        <v>0.74</v>
       </c>
       <c r="D116" t="n">
-        <v>0.65625</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="117">
@@ -4571,13 +4571,13 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.761979</v>
+        <v>0.76</v>
       </c>
       <c r="C117" t="n">
-        <v>0.649141</v>
+        <v>0.65</v>
       </c>
       <c r="D117" t="n">
-        <v>0.69684</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="118">
@@ -4587,13 +4587,13 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.547304</v>
+        <v>0.55</v>
       </c>
       <c r="C118" t="n">
-        <v>0.37173</v>
+        <v>0.37</v>
       </c>
       <c r="D118" t="n">
-        <v>0.596418</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="119">
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.53968</v>
+        <v>0.54</v>
       </c>
       <c r="C119" t="n">
-        <v>0.487797</v>
+        <v>0.49</v>
       </c>
       <c r="D119" t="n">
-        <v>0.306703</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="120">
@@ -4619,13 +4619,13 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.486994</v>
+        <v>0.49</v>
       </c>
       <c r="C120" t="n">
-        <v>0.275099</v>
+        <v>0.28</v>
       </c>
       <c r="D120" t="n">
-        <v>0.387758</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="121">
@@ -4635,13 +4635,13 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.394871</v>
+        <v>0.4</v>
       </c>
       <c r="C121" t="n">
-        <v>0.292137</v>
+        <v>0.29</v>
       </c>
       <c r="D121" t="n">
-        <v>0.243882</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="122">
@@ -4651,13 +4651,13 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.509294</v>
+        <v>0.51</v>
       </c>
       <c r="C122" t="n">
-        <v>0.348973</v>
+        <v>0.35</v>
       </c>
       <c r="D122" t="n">
-        <v>0.415141</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="123">
@@ -4667,13 +4667,13 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.7542450000000001</v>
+        <v>0.75</v>
       </c>
       <c r="C123" t="n">
-        <v>0.773361</v>
+        <v>0.77</v>
       </c>
       <c r="D123" t="n">
-        <v>0.658192</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="124">
@@ -4683,13 +4683,13 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.644508</v>
+        <v>0.64</v>
       </c>
       <c r="C124" t="n">
-        <v>0.535998</v>
+        <v>0.54</v>
       </c>
       <c r="D124" t="n">
-        <v>0.491142</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="125">
@@ -4699,13 +4699,13 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.450824</v>
+        <v>0.45</v>
       </c>
       <c r="C125" t="n">
-        <v>0.472456</v>
+        <v>0.47</v>
       </c>
       <c r="D125" t="n">
-        <v>0.587453</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="128">
@@ -4722,13 +4722,13 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.314666</v>
+        <v>0.31</v>
       </c>
       <c r="C130" t="n">
-        <v>0.363279</v>
+        <v>0.36</v>
       </c>
       <c r="D130" t="n">
-        <v>0.322055</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="131">
@@ -4738,13 +4738,13 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.361477</v>
+        <v>0.36</v>
       </c>
       <c r="C131" t="n">
-        <v>0.307947</v>
+        <v>0.31</v>
       </c>
       <c r="D131" t="n">
-        <v>0.330576</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="132">
@@ -4754,13 +4754,13 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.361149</v>
+        <v>0.36</v>
       </c>
       <c r="C132" t="n">
-        <v>0.245293</v>
+        <v>0.25</v>
       </c>
       <c r="D132" t="n">
-        <v>0.393558</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="133">
@@ -4770,13 +4770,13 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.404503</v>
+        <v>0.4</v>
       </c>
       <c r="C133" t="n">
-        <v>0.365615</v>
+        <v>0.37</v>
       </c>
       <c r="D133" t="n">
-        <v>0.229881</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="134">
@@ -4786,13 +4786,13 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.423528</v>
+        <v>0.42</v>
       </c>
       <c r="C134" t="n">
-        <v>0.239248</v>
+        <v>0.24</v>
       </c>
       <c r="D134" t="n">
-        <v>0.337224</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="135">
@@ -4802,13 +4802,13 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.424186</v>
+        <v>0.42</v>
       </c>
       <c r="C135" t="n">
-        <v>0.313825</v>
+        <v>0.31</v>
       </c>
       <c r="D135" t="n">
-        <v>0.261988</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="136">
@@ -4818,13 +4818,13 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.399946</v>
+        <v>0.4</v>
       </c>
       <c r="C136" t="n">
-        <v>0.274046</v>
+        <v>0.27</v>
       </c>
       <c r="D136" t="n">
-        <v>0.326008</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="137">
@@ -4834,13 +4834,13 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.345066</v>
+        <v>0.35</v>
       </c>
       <c r="C137" t="n">
-        <v>0.353812</v>
+        <v>0.35</v>
       </c>
       <c r="D137" t="n">
-        <v>0.301122</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="138">
@@ -4850,13 +4850,13 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.385553</v>
+        <v>0.39</v>
       </c>
       <c r="C138" t="n">
-        <v>0.32064</v>
+        <v>0.32</v>
       </c>
       <c r="D138" t="n">
-        <v>0.293807</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="139">
@@ -4866,13 +4866,13 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.298414</v>
+        <v>0.3</v>
       </c>
       <c r="C139" t="n">
-        <v>0.312733</v>
+        <v>0.31</v>
       </c>
       <c r="D139" t="n">
-        <v>0.388853</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="142">
@@ -4889,13 +4889,13 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.3088</v>
+        <v>0.31</v>
       </c>
       <c r="C144" t="n">
-        <v>0.337967</v>
+        <v>0.34</v>
       </c>
       <c r="D144" t="n">
-        <v>0.353233</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="145">
@@ -4905,13 +4905,13 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.336886</v>
+        <v>0.34</v>
       </c>
       <c r="C145" t="n">
-        <v>0.304768</v>
+        <v>0.3</v>
       </c>
       <c r="D145" t="n">
-        <v>0.358345</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="146">
@@ -4921,13 +4921,13 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.33669</v>
+        <v>0.34</v>
       </c>
       <c r="C146" t="n">
-        <v>0.267176</v>
+        <v>0.27</v>
       </c>
       <c r="D146" t="n">
-        <v>0.396135</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="147">
@@ -4937,13 +4937,13 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.362702</v>
+        <v>0.36</v>
       </c>
       <c r="C147" t="n">
-        <v>0.339369</v>
+        <v>0.34</v>
       </c>
       <c r="D147" t="n">
-        <v>0.297929</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="148">
@@ -4953,13 +4953,13 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.374117</v>
+        <v>0.37</v>
       </c>
       <c r="C148" t="n">
-        <v>0.263549</v>
+        <v>0.26</v>
       </c>
       <c r="D148" t="n">
-        <v>0.362335</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="149">
@@ -4969,13 +4969,13 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.374512</v>
+        <v>0.37</v>
       </c>
       <c r="C149" t="n">
-        <v>0.308295</v>
+        <v>0.31</v>
       </c>
       <c r="D149" t="n">
-        <v>0.317193</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="150">
@@ -4985,13 +4985,13 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.359967</v>
+        <v>0.36</v>
       </c>
       <c r="C150" t="n">
-        <v>0.284428</v>
+        <v>0.28</v>
       </c>
       <c r="D150" t="n">
-        <v>0.355605</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="151">
@@ -5001,13 +5001,13 @@
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.32704</v>
+        <v>0.33</v>
       </c>
       <c r="C151" t="n">
-        <v>0.332287</v>
+        <v>0.33</v>
       </c>
       <c r="D151" t="n">
-        <v>0.340673</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="152">
@@ -5017,13 +5017,13 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.351332</v>
+        <v>0.35</v>
       </c>
       <c r="C152" t="n">
-        <v>0.312384</v>
+        <v>0.31</v>
       </c>
       <c r="D152" t="n">
-        <v>0.336284</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="153">
@@ -5033,13 +5033,13 @@
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.299049</v>
+        <v>0.3</v>
       </c>
       <c r="C153" t="n">
-        <v>0.30764</v>
+        <v>0.31</v>
       </c>
       <c r="D153" t="n">
-        <v>0.393312</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="156">
@@ -5123,49 +5123,49 @@
         </is>
       </c>
       <c r="C159" t="n">
-        <v>5.203</v>
+        <v>5.2</v>
       </c>
       <c r="D159" t="n">
-        <v>10.736</v>
+        <v>10.74</v>
       </c>
       <c r="E159" t="n">
-        <v>14.801</v>
+        <v>14.8</v>
       </c>
       <c r="F159" t="n">
-        <v>20.071</v>
+        <v>20.07</v>
       </c>
       <c r="G159" t="n">
-        <v>6.758</v>
+        <v>6.75</v>
       </c>
       <c r="H159" t="n">
-        <v>10.736</v>
+        <v>10.74</v>
       </c>
       <c r="I159" t="n">
-        <v>14.801</v>
+        <v>14.8</v>
       </c>
       <c r="J159" t="n">
         <v>18.32</v>
       </c>
       <c r="K159" t="n">
-        <v>9.629</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="L159" t="n">
-        <v>15.855</v>
+        <v>15.85</v>
       </c>
       <c r="M159" t="n">
         <v>9.94</v>
       </c>
       <c r="N159" t="n">
-        <v>15.505</v>
+        <v>15.5</v>
       </c>
       <c r="O159" t="n">
-        <v>12.742</v>
+        <v>12.74</v>
       </c>
       <c r="P159" t="n">
-        <v>12.723</v>
+        <v>12.72</v>
       </c>
       <c r="Q159" t="n">
-        <v>12.732</v>
+        <v>12.73</v>
       </c>
     </row>
     <row r="160">
@@ -5178,49 +5178,49 @@
         </is>
       </c>
       <c r="C160" t="n">
-        <v>5.214</v>
+        <v>5.2</v>
       </c>
       <c r="D160" t="n">
-        <v>9.804</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="E160" t="n">
-        <v>14.726</v>
+        <v>14.73</v>
       </c>
       <c r="F160" t="n">
         <v>21.53</v>
       </c>
       <c r="G160" t="n">
-        <v>6.622</v>
+        <v>6.62</v>
       </c>
       <c r="H160" t="n">
-        <v>9.804</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I160" t="n">
-        <v>14.726</v>
+        <v>14.73</v>
       </c>
       <c r="J160" t="n">
-        <v>19.217</v>
+        <v>19.22</v>
       </c>
       <c r="K160" t="n">
-        <v>8.885999999999999</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="L160" t="n">
-        <v>16.087</v>
+        <v>16.09</v>
       </c>
       <c r="M160" t="n">
-        <v>9.167999999999999</v>
+        <v>9.16</v>
       </c>
       <c r="N160" t="n">
-        <v>15.624</v>
+        <v>15.63</v>
       </c>
       <c r="O160" t="n">
-        <v>12.486</v>
+        <v>12.48</v>
       </c>
       <c r="P160" t="n">
-        <v>12.396</v>
+        <v>12.4</v>
       </c>
       <c r="Q160" t="n">
-        <v>12.441</v>
+        <v>12.44</v>
       </c>
     </row>
     <row r="161">
@@ -5233,49 +5233,49 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>4.654</v>
+        <v>4.65</v>
       </c>
       <c r="D161" t="n">
-        <v>9.768000000000001</v>
+        <v>9.77</v>
       </c>
       <c r="E161" t="n">
-        <v>14.175</v>
+        <v>14.18</v>
       </c>
       <c r="F161" t="n">
-        <v>19.712</v>
+        <v>19.72</v>
       </c>
       <c r="G161" t="n">
-        <v>6.041</v>
+        <v>6.04</v>
       </c>
       <c r="H161" t="n">
-        <v>9.768000000000001</v>
+        <v>9.77</v>
       </c>
       <c r="I161" t="n">
-        <v>14.175</v>
+        <v>14.18</v>
       </c>
       <c r="J161" t="n">
-        <v>17.875</v>
+        <v>17.88</v>
       </c>
       <c r="K161" t="n">
-        <v>8.744999999999999</v>
+        <v>8.75</v>
       </c>
       <c r="L161" t="n">
-        <v>15.282</v>
+        <v>15.29</v>
       </c>
       <c r="M161" t="n">
-        <v>9.023</v>
+        <v>9.02</v>
       </c>
       <c r="N161" t="n">
-        <v>14.915</v>
+        <v>14.92</v>
       </c>
       <c r="O161" t="n">
-        <v>12.014</v>
+        <v>12.02</v>
       </c>
       <c r="P161" t="n">
-        <v>11.969</v>
+        <v>11.97</v>
       </c>
       <c r="Q161" t="n">
-        <v>11.991</v>
+        <v>12</v>
       </c>
     </row>
     <row r="162">
@@ -5288,49 +5288,49 @@
         </is>
       </c>
       <c r="C162" t="n">
-        <v>4.789</v>
+        <v>4.79</v>
       </c>
       <c r="D162" t="n">
-        <v>9.646000000000001</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="E162" t="n">
-        <v>14.106</v>
+        <v>14.11</v>
       </c>
       <c r="F162" t="n">
-        <v>19.779</v>
+        <v>19.78</v>
       </c>
       <c r="G162" t="n">
-        <v>6.104</v>
+        <v>6.1</v>
       </c>
       <c r="H162" t="n">
-        <v>9.646000000000001</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="I162" t="n">
-        <v>14.106</v>
+        <v>14.11</v>
       </c>
       <c r="J162" t="n">
-        <v>17.892</v>
+        <v>17.89</v>
       </c>
       <c r="K162" t="n">
-        <v>8.675000000000001</v>
+        <v>8.67</v>
       </c>
       <c r="L162" t="n">
-        <v>15.241</v>
+        <v>15.24</v>
       </c>
       <c r="M162" t="n">
-        <v>8.938000000000001</v>
+        <v>8.93</v>
       </c>
       <c r="N162" t="n">
-        <v>14.863</v>
+        <v>14.87</v>
       </c>
       <c r="O162" t="n">
-        <v>11.958</v>
+        <v>11.96</v>
       </c>
       <c r="P162" t="n">
-        <v>11.901</v>
+        <v>11.9</v>
       </c>
       <c r="Q162" t="n">
-        <v>11.929</v>
+        <v>11.93</v>
       </c>
     </row>
     <row r="163">
@@ -5343,49 +5343,49 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>4.52</v>
+        <v>4.51</v>
       </c>
       <c r="D163" t="n">
-        <v>9.212999999999999</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="E163" t="n">
-        <v>13.965</v>
+        <v>13.96</v>
       </c>
       <c r="F163" t="n">
-        <v>20.144</v>
+        <v>20.15</v>
       </c>
       <c r="G163" t="n">
-        <v>5.866</v>
+        <v>5.86</v>
       </c>
       <c r="H163" t="n">
-        <v>9.212999999999999</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="I163" t="n">
-        <v>13.965</v>
+        <v>13.96</v>
       </c>
       <c r="J163" t="n">
-        <v>18.071</v>
+        <v>18.07</v>
       </c>
       <c r="K163" t="n">
-        <v>8.273999999999999</v>
+        <v>8.27</v>
       </c>
       <c r="L163" t="n">
-        <v>15.201</v>
+        <v>15.2</v>
       </c>
       <c r="M163" t="n">
-        <v>8.544</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="N163" t="n">
-        <v>14.786</v>
+        <v>14.78</v>
       </c>
       <c r="O163" t="n">
-        <v>11.738</v>
+        <v>11.73</v>
       </c>
       <c r="P163" t="n">
-        <v>11.665</v>
+        <v>11.66</v>
       </c>
       <c r="Q163" t="n">
-        <v>11.701</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="164">
@@ -5398,49 +5398,49 @@
         </is>
       </c>
       <c r="C164" t="n">
-        <v>4.004</v>
+        <v>4</v>
       </c>
       <c r="D164" t="n">
-        <v>8.766999999999999</v>
+        <v>8.76</v>
       </c>
       <c r="E164" t="n">
-        <v>13.438</v>
+        <v>13.43</v>
       </c>
       <c r="F164" t="n">
-        <v>19.216</v>
+        <v>19.22</v>
       </c>
       <c r="G164" t="n">
-        <v>5.292</v>
+        <v>5.29</v>
       </c>
       <c r="H164" t="n">
-        <v>8.766999999999999</v>
+        <v>8.76</v>
       </c>
       <c r="I164" t="n">
-        <v>13.438</v>
+        <v>13.43</v>
       </c>
       <c r="J164" t="n">
-        <v>17.299</v>
+        <v>17.3</v>
       </c>
       <c r="K164" t="n">
-        <v>7.814</v>
+        <v>7.81</v>
       </c>
       <c r="L164" t="n">
-        <v>14.594</v>
+        <v>14.59</v>
       </c>
       <c r="M164" t="n">
-        <v>8.071999999999999</v>
+        <v>8.07</v>
       </c>
       <c r="N164" t="n">
-        <v>14.21</v>
+        <v>14.2</v>
       </c>
       <c r="O164" t="n">
-        <v>11.204</v>
+        <v>11.2</v>
       </c>
       <c r="P164" t="n">
-        <v>11.141</v>
+        <v>11.13</v>
       </c>
       <c r="Q164" t="n">
-        <v>11.172</v>
+        <v>11.17</v>
       </c>
     </row>
     <row r="165">
@@ -5453,49 +5453,49 @@
         </is>
       </c>
       <c r="C165" t="n">
-        <v>4.146</v>
+        <v>4.15</v>
       </c>
       <c r="D165" t="n">
-        <v>8.779</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="E165" t="n">
-        <v>13.123</v>
+        <v>13.12</v>
       </c>
       <c r="F165" t="n">
-        <v>18.362</v>
+        <v>18.36</v>
       </c>
       <c r="G165" t="n">
-        <v>5.301</v>
+        <v>5.3</v>
       </c>
       <c r="H165" t="n">
-        <v>8.779</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="I165" t="n">
-        <v>13.123</v>
+        <v>13.12</v>
       </c>
       <c r="J165" t="n">
-        <v>16.641</v>
+        <v>16.64</v>
       </c>
       <c r="K165" t="n">
-        <v>7.852</v>
+        <v>7.85</v>
       </c>
       <c r="L165" t="n">
-        <v>14.171</v>
+        <v>14.17</v>
       </c>
       <c r="M165" t="n">
-        <v>8.083</v>
+        <v>8.08</v>
       </c>
       <c r="N165" t="n">
-        <v>13.827</v>
+        <v>13.82</v>
       </c>
       <c r="O165" t="n">
-        <v>11.011</v>
+        <v>11.01</v>
       </c>
       <c r="P165" t="n">
-        <v>10.955</v>
+        <v>10.95</v>
       </c>
       <c r="Q165" t="n">
-        <v>10.983</v>
+        <v>10.98</v>
       </c>
     </row>
     <row r="166">
@@ -5508,49 +5508,49 @@
         </is>
       </c>
       <c r="C166" t="n">
-        <v>3.868</v>
+        <v>3.86</v>
       </c>
       <c r="D166" t="n">
-        <v>8.645</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="E166" t="n">
-        <v>13.168</v>
+        <v>13.17</v>
       </c>
       <c r="F166" t="n">
-        <v>18.638</v>
+        <v>18.64</v>
       </c>
       <c r="G166" t="n">
-        <v>5.132</v>
+        <v>5.13</v>
       </c>
       <c r="H166" t="n">
-        <v>8.645</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="I166" t="n">
-        <v>13.168</v>
+        <v>13.17</v>
       </c>
       <c r="J166" t="n">
-        <v>16.833</v>
+        <v>16.83</v>
       </c>
       <c r="K166" t="n">
-        <v>7.69</v>
+        <v>7.68</v>
       </c>
       <c r="L166" t="n">
-        <v>14.262</v>
+        <v>14.26</v>
       </c>
       <c r="M166" t="n">
-        <v>7.942</v>
+        <v>7.94</v>
       </c>
       <c r="N166" t="n">
-        <v>13.901</v>
+        <v>13.9</v>
       </c>
       <c r="O166" t="n">
-        <v>10.976</v>
+        <v>10.97</v>
       </c>
       <c r="P166" t="n">
-        <v>10.921</v>
+        <v>10.92</v>
       </c>
       <c r="Q166" t="n">
-        <v>10.949</v>
+        <v>10.95</v>
       </c>
     </row>
     <row r="167">
@@ -5563,13 +5563,13 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>3.944</v>
+        <v>3.95</v>
       </c>
       <c r="D167" t="n">
-        <v>8.468</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="E167" t="n">
-        <v>12.758</v>
+        <v>12.76</v>
       </c>
       <c r="F167" t="n">
         <v>17.83</v>
@@ -5578,19 +5578,19 @@
         <v>5.03</v>
       </c>
       <c r="H167" t="n">
-        <v>8.468</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="I167" t="n">
-        <v>12.758</v>
+        <v>12.76</v>
       </c>
       <c r="J167" t="n">
         <v>16.17</v>
       </c>
       <c r="K167" t="n">
-        <v>7.563</v>
+        <v>7.57</v>
       </c>
       <c r="L167" t="n">
-        <v>13.772</v>
+        <v>13.77</v>
       </c>
       <c r="M167" t="n">
         <v>7.78</v>
@@ -5599,13 +5599,13 @@
         <v>13.44</v>
       </c>
       <c r="O167" t="n">
-        <v>10.668</v>
+        <v>10.67</v>
       </c>
       <c r="P167" t="n">
         <v>10.61</v>
       </c>
       <c r="Q167" t="n">
-        <v>10.639</v>
+        <v>10.64</v>
       </c>
     </row>
     <row r="168">
@@ -5618,10 +5618,10 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>0.958</v>
+        <v>0.96</v>
       </c>
       <c r="D168" t="n">
-        <v>4.495</v>
+        <v>4.49</v>
       </c>
       <c r="E168" t="n">
         <v>9.449999999999999</v>
@@ -5630,37 +5630,37 @@
         <v>14.46</v>
       </c>
       <c r="G168" t="n">
-        <v>1.579</v>
+        <v>1.57</v>
       </c>
       <c r="H168" t="n">
-        <v>4.495</v>
+        <v>4.49</v>
       </c>
       <c r="I168" t="n">
         <v>9.449999999999999</v>
       </c>
       <c r="J168" t="n">
-        <v>12.864</v>
+        <v>12.86</v>
       </c>
       <c r="K168" t="n">
-        <v>3.788</v>
+        <v>3.78</v>
       </c>
       <c r="L168" t="n">
-        <v>10.452</v>
+        <v>10.45</v>
       </c>
       <c r="M168" t="n">
-        <v>3.912</v>
+        <v>3.91</v>
       </c>
       <c r="N168" t="n">
-        <v>10.133</v>
+        <v>10.13</v>
       </c>
       <c r="O168" t="n">
         <v>7.12</v>
       </c>
       <c r="P168" t="n">
-        <v>7.022</v>
+        <v>7.02</v>
       </c>
       <c r="Q168" t="n">
-        <v>7.071</v>
+        <v>7.07</v>
       </c>
     </row>
   </sheetData>
